--- a/exports/trend_1d/NAVINFLUOR_full_report.xlsx
+++ b/exports/trend_1d/NAVINFLUOR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="H2" t="n">
-        <v>164.38</v>
+        <v>163.13</v>
       </c>
       <c r="I2" t="n">
         <v>164.0018298641475</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K2" t="n">
-        <v>27.18</v>
+        <v>26.21</v>
       </c>
       <c r="L2" t="n">
         <v>1.28</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>18.52</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42156</v>
+        <v>42157</v>
       </c>
       <c r="H3" t="n">
-        <v>183.18</v>
+        <v>185.08</v>
       </c>
       <c r="I3" t="n">
         <v>183.5458520279491</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.29</v>
+        <v>-13.46</v>
       </c>
       <c r="L3" t="n">
-        <v>13.64</v>
+        <v>14.96</v>
       </c>
       <c r="M3" t="n">
         <v>2.34</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>275.45</v>
+        <v>231.12</v>
       </c>
       <c r="I4" t="n">
         <v>238.0487860454749</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K4" t="n">
-        <v>48.83</v>
+        <v>24.88</v>
       </c>
       <c r="L4" t="n">
         <v>7.75</v>
       </c>
       <c r="M4" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.19</v>
+        <v>16.09</v>
       </c>
       <c r="O4" t="n">
         <v>1.04</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>29.96</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42290</v>
+        <v>42291</v>
       </c>
       <c r="H5" t="n">
-        <v>262.36</v>
+        <v>266.02</v>
       </c>
       <c r="I5" t="n">
         <v>265.1124188705594</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.52</v>
+        <v>-15.1</v>
       </c>
       <c r="L5" t="n">
         <v>20.96</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>13.16</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H6" t="n">
-        <v>359.25</v>
+        <v>333.89</v>
       </c>
       <c r="I6" t="n">
         <v>339.0552668855615</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K6" t="n">
-        <v>35.05</v>
+        <v>25.51</v>
       </c>
       <c r="L6" t="n">
         <v>4.14</v>
       </c>
       <c r="M6" t="n">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>7.06</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>23.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42451</v>
+        <v>42452</v>
       </c>
       <c r="H7" t="n">
-        <v>282.96</v>
+        <v>339.55</v>
       </c>
       <c r="I7" t="n">
         <v>309.7900442274127</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K7" t="n">
-        <v>15.25</v>
+        <v>-1.7</v>
       </c>
       <c r="L7" t="n">
         <v>10.33</v>
@@ -840,7 +923,7 @@
         <v>3.13</v>
       </c>
       <c r="N7" t="n">
-        <v>7.43</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
         <v>-7.06</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>20.49</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42675</v>
+        <v>42676</v>
       </c>
       <c r="H8" t="n">
-        <v>499.16</v>
+        <v>490.68</v>
       </c>
       <c r="I8" t="n">
         <v>497.0972508204266</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K8" t="n">
-        <v>47.01</v>
+        <v>44.51</v>
       </c>
       <c r="L8" t="n">
         <v>15.18</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>14.34</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H9" t="n">
-        <v>508.69</v>
+        <v>516.78</v>
       </c>
       <c r="I9" t="n">
         <v>512.5786191700299</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.67</v>
+        <v>-5.32</v>
       </c>
       <c r="L9" t="n">
-        <v>5.93</v>
+        <v>11.24</v>
       </c>
       <c r="M9" t="n">
         <v>2.22</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42776</v>
+        <v>42779</v>
       </c>
       <c r="H10" t="n">
-        <v>525.29</v>
+        <v>516.48</v>
       </c>
       <c r="I10" t="n">
         <v>523.1639803000031</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>1.65</v>
+        <v>-0.06</v>
       </c>
       <c r="L10" t="n">
         <v>1.89</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.43</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42810</v>
+        <v>42811</v>
       </c>
       <c r="H11" t="n">
-        <v>535.17</v>
+        <v>546.65</v>
       </c>
       <c r="I11" t="n">
         <v>544.7452647626568</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.62</v>
+        <v>-5.84</v>
       </c>
       <c r="L11" t="n">
-        <v>4.28</v>
+        <v>6.14</v>
       </c>
       <c r="M11" t="n">
         <v>1.77</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H12" t="n">
-        <v>599.1</v>
+        <v>592.99</v>
       </c>
       <c r="I12" t="n">
         <v>594.0032181702436</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
-        <v>9.59</v>
+        <v>8.48</v>
       </c>
       <c r="L12" t="n">
         <v>2.83</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.9</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H13" t="n">
-        <v>625.15</v>
+        <v>635.17</v>
       </c>
       <c r="I13" t="n">
         <v>631.5833508203939</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.42</v>
+        <v>-7.11</v>
       </c>
       <c r="L13" t="n">
-        <v>5.7</v>
+        <v>7.92</v>
       </c>
       <c r="M13" t="n">
         <v>1.15</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.85</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H14" t="n">
-        <v>687.3</v>
+        <v>654.05</v>
       </c>
       <c r="I14" t="n">
         <v>676.8791367941297</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K14" t="n">
-        <v>8.210000000000001</v>
+        <v>2.97</v>
       </c>
       <c r="L14" t="n">
         <v>9.109999999999999</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.41</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43006</v>
+        <v>43007</v>
       </c>
       <c r="H15" t="n">
-        <v>666.15</v>
+        <v>698.15</v>
       </c>
       <c r="I15" t="n">
         <v>684.516162473921</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.85</v>
+        <v>-6.74</v>
       </c>
       <c r="L15" t="n">
         <v>9.93</v>
@@ -1296,7 +1475,7 @@
         <v>1.64</v>
       </c>
       <c r="N15" t="n">
-        <v>4.01</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
         <v>-4.84</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.54</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43151</v>
+        <v>43152</v>
       </c>
       <c r="H16" t="n">
-        <v>763.85</v>
+        <v>743.85</v>
       </c>
       <c r="I16" t="n">
         <v>763.2703104549852</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K16" t="n">
-        <v>9.41</v>
+        <v>6.55</v>
       </c>
       <c r="L16" t="n">
         <v>5.46</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.89</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43305</v>
+        <v>43306</v>
       </c>
       <c r="H17" t="n">
-        <v>599.45</v>
+        <v>675.9</v>
       </c>
       <c r="I17" t="n">
         <v>663.4221705243799</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K17" t="n">
-        <v>19.41</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>12.93</v>
@@ -1410,7 +1613,7 @@
         <v>2.4</v>
       </c>
       <c r="N17" t="n">
-        <v>5.88</v>
+        <v>12.75</v>
       </c>
       <c r="O17" t="n">
         <v>-2.62</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H18" t="n">
-        <v>667.95</v>
+        <v>657.3</v>
       </c>
       <c r="I18" t="n">
         <v>666.6990921703107</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.18</v>
+        <v>-2.75</v>
       </c>
       <c r="L18" t="n">
         <v>11.85</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>13.26</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43425</v>
+        <v>43426</v>
       </c>
       <c r="H19" t="n">
-        <v>685.5</v>
+        <v>714.95</v>
       </c>
       <c r="I19" t="n">
         <v>703.3435429443136</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.29</v>
+        <v>-8.77</v>
       </c>
       <c r="L19" t="n">
-        <v>6.19</v>
+        <v>9.08</v>
       </c>
       <c r="M19" t="n">
         <v>2.57</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.71</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43482</v>
+        <v>43483</v>
       </c>
       <c r="H20" t="n">
-        <v>667.05</v>
+        <v>661.75</v>
       </c>
       <c r="I20" t="n">
         <v>663.9276290912435</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.7</v>
+        <v>-7.44</v>
       </c>
       <c r="L20" t="n">
         <v>8.369999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.94</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H21" t="n">
-        <v>600.3</v>
+        <v>644.1</v>
       </c>
       <c r="I21" t="n">
         <v>642.7944307753685</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K21" t="n">
-        <v>9.289999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="L21" t="n">
         <v>1.89</v>
@@ -1638,7 +1889,7 @@
         <v>1.61</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>7.3</v>
       </c>
       <c r="O21" t="n">
         <v>-0.79</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H22" t="n">
-        <v>703.95</v>
+        <v>693.7</v>
       </c>
       <c r="I22" t="n">
         <v>697.9430430324763</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K22" t="n">
-        <v>9.289999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L22" t="n">
         <v>7.15</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H23" t="n">
-        <v>699.45</v>
+        <v>739.65</v>
       </c>
       <c r="I23" t="n">
         <v>714.5204702493343</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.83</v>
+        <v>-6.62</v>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>8.51</v>
       </c>
       <c r="M23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="N23" t="n">
-        <v>1.94</v>
+        <v>5.75</v>
       </c>
       <c r="O23" t="n">
         <v>-1.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.03</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H24" t="n">
-        <v>700.6</v>
+        <v>673.1</v>
       </c>
       <c r="I24" t="n">
         <v>681.4395768800596</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.28</v>
+        <v>-9</v>
       </c>
       <c r="L24" t="n">
-        <v>6.71</v>
+        <v>9.27</v>
       </c>
       <c r="M24" t="n">
         <v>1.68</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>3.93</v>
       </c>
       <c r="O24" t="n">
         <v>5.75</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.94</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43683</v>
+        <v>43684</v>
       </c>
       <c r="H25" t="n">
-        <v>646</v>
+        <v>670.1</v>
       </c>
       <c r="I25" t="n">
         <v>649.2231277262836</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>4.03</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
         <v>4.99</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H26" t="n">
-        <v>724.55</v>
+        <v>697</v>
       </c>
       <c r="I26" t="n">
         <v>702.5992102278906</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K26" t="n">
-        <v>8.130000000000001</v>
+        <v>4.01</v>
       </c>
       <c r="L26" t="n">
         <v>5.23</v>
@@ -1923,7 +2234,7 @@
         <v>1.72</v>
       </c>
       <c r="N26" t="n">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>3.73</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>16.83</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H27" t="n">
-        <v>759.95</v>
+        <v>825.55</v>
       </c>
       <c r="I27" t="n">
         <v>785.2006901944964</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.029999999999999</v>
+        <v>-18.44</v>
       </c>
       <c r="L27" t="n">
-        <v>13.06</v>
+        <v>19.37</v>
       </c>
       <c r="M27" t="n">
-        <v>0.99</v>
+        <v>4.35</v>
       </c>
       <c r="N27" t="n">
-        <v>3.04</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-3.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.97</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43906</v>
+        <v>43907</v>
       </c>
       <c r="H28" t="n">
-        <v>1296.95</v>
+        <v>1290.2</v>
       </c>
       <c r="I28" t="n">
         <v>1294.14196371434</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K28" t="n">
-        <v>57.1</v>
+        <v>56.28</v>
       </c>
       <c r="L28" t="n">
         <v>5.51</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>32.26</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H29" t="n">
-        <v>1465.6</v>
+        <v>1534.35</v>
       </c>
       <c r="I29" t="n">
         <v>1501.552934430267</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-13.59</v>
+        <v>-18.92</v>
       </c>
       <c r="L29" t="n">
-        <v>16.26</v>
+        <v>20.52</v>
       </c>
       <c r="M29" t="n">
         <v>9.34</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>24.47</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H30" t="n">
-        <v>2546.15</v>
+        <v>2496.95</v>
       </c>
       <c r="I30" t="n">
         <v>2534.20934923902</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K30" t="n">
-        <v>65.94</v>
+        <v>62.74</v>
       </c>
       <c r="L30" t="n">
         <v>10.39</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.78</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44253</v>
+        <v>44256</v>
       </c>
       <c r="H31" t="n">
-        <v>2544.9</v>
+        <v>2657.5</v>
       </c>
       <c r="I31" t="n">
         <v>2641.570280728558</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.92</v>
+        <v>-6.43</v>
       </c>
       <c r="L31" t="n">
-        <v>6.93</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>1.54</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.35</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H32" t="n">
-        <v>2486.9</v>
+        <v>2447.4</v>
       </c>
       <c r="I32" t="n">
         <v>2452.656289680689</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.42</v>
+        <v>-7.91</v>
       </c>
       <c r="L32" t="n">
         <v>10.09</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44291</v>
+        <v>44292</v>
       </c>
       <c r="H33" t="n">
-        <v>2739.6</v>
+        <v>2926.65</v>
       </c>
       <c r="I33" t="n">
         <v>2778.344432930333</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.94</v>
+        <v>-19.58</v>
       </c>
       <c r="L33" t="n">
-        <v>15.22</v>
+        <v>21.56</v>
       </c>
       <c r="M33" t="n">
         <v>1.49</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.48</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="H34" t="n">
-        <v>3681.25</v>
+        <v>3515.85</v>
       </c>
       <c r="I34" t="n">
         <v>3595.096140192358</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K34" t="n">
-        <v>25.78</v>
+        <v>20.13</v>
       </c>
       <c r="L34" t="n">
         <v>7.23</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>14.53</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H35" t="n">
-        <v>3924.7</v>
+        <v>4027.6</v>
       </c>
       <c r="I35" t="n">
         <v>3950.504987419794</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.63</v>
+        <v>-14.56</v>
       </c>
       <c r="L35" t="n">
-        <v>13.17</v>
+        <v>16.01</v>
       </c>
       <c r="M35" t="n">
         <v>1.3</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44456</v>
+        <v>44459</v>
       </c>
       <c r="H36" t="n">
-        <v>3860.15</v>
+        <v>3713.85</v>
       </c>
       <c r="I36" t="n">
         <v>3771.964924112284</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.16</v>
+        <v>-7.79</v>
       </c>
       <c r="L36" t="n">
-        <v>4.41</v>
+        <v>7.98</v>
       </c>
       <c r="M36" t="n">
-        <v>0.08</v>
+        <v>0.78</v>
       </c>
       <c r="N36" t="n">
         <v>4.18</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44532</v>
+        <v>44533</v>
       </c>
       <c r="H37" t="n">
-        <v>3780.2</v>
+        <v>3831.6</v>
       </c>
       <c r="I37" t="n">
         <v>3790.07341664884</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.79</v>
+        <v>-3.17</v>
       </c>
       <c r="L37" t="n">
         <v>11.91</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.7</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H38" t="n">
-        <v>4031.85</v>
+        <v>3869.15</v>
       </c>
       <c r="I38" t="n">
         <v>3879.104546867851</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>5.23</v>
+        <v>0.98</v>
       </c>
       <c r="L38" t="n">
         <v>2.18</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>11.89</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H39" t="n">
-        <v>3934.3</v>
+        <v>4256.8</v>
       </c>
       <c r="I39" t="n">
         <v>4187.682582958002</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.68</v>
+        <v>-10.02</v>
       </c>
       <c r="L39" t="n">
-        <v>4.43</v>
+        <v>11.85</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>-4.04</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>17.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H40" t="n">
-        <v>3811.25</v>
+        <v>3679.3</v>
       </c>
       <c r="I40" t="n">
         <v>3698.206475589129</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.47</v>
+        <v>-13.57</v>
       </c>
       <c r="L40" t="n">
-        <v>13.39</v>
+        <v>14.69</v>
       </c>
       <c r="M40" t="n">
         <v>3.43</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>13.41</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H41" t="n">
-        <v>3954.3</v>
+        <v>4087.4</v>
       </c>
       <c r="I41" t="n">
         <v>3969.937979536428</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.47</v>
+        <v>-11.09</v>
       </c>
       <c r="L41" t="n">
-        <v>9.26</v>
+        <v>12.25</v>
       </c>
       <c r="M41" t="n">
         <v>2.49</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>12.78</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H42" t="n">
-        <v>3790.5</v>
+        <v>3745.6</v>
       </c>
       <c r="I42" t="n">
         <v>3767.041034392059</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.26</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>8.25</v>
+        <v>9.57</v>
       </c>
       <c r="M42" t="n">
-        <v>0.82</v>
+        <v>2.39</v>
       </c>
       <c r="N42" t="n">
         <v>3.98</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>11.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H43" t="n">
-        <v>3787.85</v>
+        <v>4208.2</v>
       </c>
       <c r="I43" t="n">
         <v>3896.948102029271</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.13</v>
+        <v>-12.35</v>
       </c>
       <c r="L43" t="n">
-        <v>7.83</v>
+        <v>13.89</v>
       </c>
       <c r="M43" t="n">
         <v>1.4</v>
       </c>
       <c r="N43" t="n">
-        <v>5.01</v>
+        <v>11.1</v>
       </c>
       <c r="O43" t="n">
         <v>-1.18</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.33</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H44" t="n">
-        <v>4419.95</v>
+        <v>4286.8</v>
       </c>
       <c r="I44" t="n">
         <v>4375.686337559862</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K44" t="n">
-        <v>5.03</v>
+        <v>1.87</v>
       </c>
       <c r="L44" t="n">
         <v>9.68</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.56</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44963</v>
+        <v>44964</v>
       </c>
       <c r="H45" t="n">
-        <v>4112.95</v>
+        <v>4281.3</v>
       </c>
       <c r="I45" t="n">
         <v>4124.855782764654</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K45" t="n">
-        <v>4.06</v>
+        <v>0.13</v>
       </c>
       <c r="L45" t="n">
         <v>8.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.48</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H46" t="n">
-        <v>4619.9</v>
+        <v>4556.05</v>
       </c>
       <c r="I46" t="n">
         <v>4558.363093158624</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K46" t="n">
-        <v>7.91</v>
+        <v>6.42</v>
       </c>
       <c r="L46" t="n">
         <v>5.8</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.97</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45138</v>
+        <v>45139</v>
       </c>
       <c r="H47" t="n">
-        <v>4264.75</v>
+        <v>4554.35</v>
       </c>
       <c r="I47" t="n">
         <v>4538.889189864453</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K47" t="n">
-        <v>6.39</v>
+        <v>0.04</v>
       </c>
       <c r="L47" t="n">
         <v>4.15</v>
@@ -3120,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.66</v>
+        <v>6.79</v>
       </c>
       <c r="O47" t="n">
         <v>-1.38</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.56</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H48" t="n">
-        <v>4444.85</v>
+        <v>4357.65</v>
       </c>
       <c r="I48" t="n">
         <v>4416.696823884385</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.4</v>
+        <v>-4.32</v>
       </c>
       <c r="L48" t="n">
         <v>7.23</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.87</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H49" t="n">
-        <v>3538.85</v>
+        <v>3636.05</v>
       </c>
       <c r="I49" t="n">
         <v>3629.90161702133</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>18.79</v>
+        <v>16.56</v>
       </c>
       <c r="L49" t="n">
         <v>2.58</v>
@@ -3234,7 +3821,7 @@
         <v>0.88</v>
       </c>
       <c r="N49" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="O49" t="n">
         <v>-1.96</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H50" t="n">
-        <v>3822.65</v>
+        <v>3609.7</v>
       </c>
       <c r="I50" t="n">
         <v>3672.650574402665</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>5.13</v>
+        <v>-0.72</v>
       </c>
       <c r="L50" t="n">
         <v>2.72</v>
@@ -3291,7 +3890,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>3.78</v>
+        <v>5.57</v>
       </c>
       <c r="O50" t="n">
         <v>2.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H51" t="n">
-        <v>3057.6</v>
+        <v>3245.7</v>
       </c>
       <c r="I51" t="n">
         <v>3179.001054586087</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K51" t="n">
-        <v>15.29</v>
+        <v>10.08</v>
       </c>
       <c r="L51" t="n">
         <v>6.05</v>
@@ -3348,7 +3959,7 @@
         <v>1.47</v>
       </c>
       <c r="N51" t="n">
-        <v>4.03</v>
+        <v>6.15</v>
       </c>
       <c r="O51" t="n">
         <v>-5.57</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.99</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H52" t="n">
-        <v>3231.2</v>
+        <v>3187.4</v>
       </c>
       <c r="I52" t="n">
         <v>3204.62552216473</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.45</v>
+        <v>-1.8</v>
       </c>
       <c r="L52" t="n">
         <v>6.43</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45453</v>
+        <v>45454</v>
       </c>
       <c r="H53" t="n">
-        <v>3435.7</v>
+        <v>3485.05</v>
       </c>
       <c r="I53" t="n">
         <v>3472.208942313209</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.79</v>
+        <v>-9.34</v>
       </c>
       <c r="L53" t="n">
-        <v>8.18</v>
+        <v>11.53</v>
       </c>
       <c r="M53" t="n">
         <v>2.75</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11.13</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H54" t="n">
-        <v>3466.9</v>
+        <v>3277.05</v>
       </c>
       <c r="I54" t="n">
         <v>3420.235396899594</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.52</v>
+        <v>-5.97</v>
       </c>
       <c r="L54" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="M54" t="n">
         <v>2.53</v>
       </c>
       <c r="N54" t="n">
-        <v>4.17</v>
+        <v>5.48</v>
       </c>
       <c r="O54" t="n">
         <v>1.44</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>14.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="H55" t="n">
-        <v>3429.25</v>
+        <v>3441.35</v>
       </c>
       <c r="I55" t="n">
         <v>3437.821072678249</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.64</v>
+        <v>-5.01</v>
       </c>
       <c r="L55" t="n">
-        <v>6.01</v>
+        <v>6.1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="N55" t="n">
         <v>2.7</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H56" t="n">
-        <v>3310.8</v>
+        <v>3221</v>
       </c>
       <c r="I56" t="n">
         <v>3268.699747317237</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.79</v>
+        <v>-6.4</v>
       </c>
       <c r="L56" t="n">
-        <v>4.6</v>
+        <v>6.91</v>
       </c>
       <c r="M56" t="n">
         <v>1.01</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H57" t="n">
-        <v>3507.9</v>
+        <v>3583</v>
       </c>
       <c r="I57" t="n">
         <v>3579.642277656825</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.91</v>
+        <v>-11.24</v>
       </c>
       <c r="L57" t="n">
-        <v>10.53</v>
+        <v>11.83</v>
       </c>
       <c r="M57" t="n">
         <v>1.83</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>9.56</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H58" t="n">
-        <v>3388.75</v>
+        <v>3305.85</v>
       </c>
       <c r="I58" t="n">
         <v>3330.996546637287</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.42</v>
+        <v>-7.74</v>
       </c>
       <c r="L58" t="n">
-        <v>5.51</v>
+        <v>8.1</v>
       </c>
       <c r="M58" t="n">
         <v>0.8</v>
       </c>
       <c r="N58" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O58" t="n">
         <v>2.14</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>10.08</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H59" t="n">
-        <v>3493.15</v>
+        <v>3824.55</v>
       </c>
       <c r="I59" t="n">
         <v>3496.84887134598</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.67</v>
+        <v>-15.69</v>
       </c>
       <c r="L59" t="n">
-        <v>6.42</v>
+        <v>21.51</v>
       </c>
       <c r="M59" t="n">
-        <v>0.83</v>
+        <v>2.78</v>
       </c>
       <c r="N59" t="n">
-        <v>3.93</v>
+        <v>9.49</v>
       </c>
       <c r="O59" t="n">
         <v>-2.45</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.34</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45713</v>
+        <v>45715</v>
       </c>
       <c r="H60" t="n">
-        <v>3809.6</v>
+        <v>3773.7</v>
       </c>
       <c r="I60" t="n">
         <v>3803.652851278282</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.39</v>
+        <v>-1.33</v>
       </c>
       <c r="L60" t="n">
         <v>8.43</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.5</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H61" t="n">
-        <v>4168.45</v>
+        <v>4246.7</v>
       </c>
       <c r="I61" t="n">
         <v>4186.270803535898</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.46</v>
+        <v>-12.53</v>
       </c>
       <c r="L61" t="n">
-        <v>12.6</v>
+        <v>13.63</v>
       </c>
       <c r="M61" t="n">
         <v>1.15</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.74</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="H62" t="n">
-        <v>3879.85</v>
+        <v>3848.6</v>
       </c>
       <c r="I62" t="n">
         <v>3865.085385537583</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.640000000000001</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>13.57</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>14.65</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45771</v>
+        <v>45772</v>
       </c>
       <c r="H63" t="n">
-        <v>4340.1</v>
+        <v>4448.7</v>
       </c>
       <c r="I63" t="n">
         <v>4412.534186149522</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.77</v>
+        <v>-15.59</v>
       </c>
       <c r="L63" t="n">
-        <v>16.28</v>
+        <v>18.54</v>
       </c>
       <c r="M63" t="n">
         <v>0.9399999999999999</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.84</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="H64" t="n">
-        <v>4796</v>
+        <v>4707</v>
       </c>
       <c r="I64" t="n">
         <v>4720.620712077872</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K64" t="n">
-        <v>7.81</v>
+        <v>5.81</v>
       </c>
       <c r="L64" t="n">
         <v>5.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.37</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="H65" t="n">
-        <v>4884.2</v>
+        <v>5057.7</v>
       </c>
       <c r="I65" t="n">
         <v>4914.515068195507</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.76</v>
+        <v>-7.45</v>
       </c>
       <c r="L65" t="n">
-        <v>6.12</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M65" t="n">
         <v>1.81</v>
       </c>
       <c r="N65" t="n">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="O65" t="n">
         <v>-1.86</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.27</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H66" t="n">
-        <v>5772</v>
+        <v>5563</v>
       </c>
       <c r="I66" t="n">
         <v>5564.13110021428</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K66" t="n">
-        <v>14.12</v>
+        <v>9.99</v>
       </c>
       <c r="L66" t="n">
         <v>3.3</v>
@@ -4203,7 +4994,7 @@
         <v>0.68</v>
       </c>
       <c r="N66" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="O66" t="n">
         <v>3.55</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H67" t="n">
-        <v>6043</v>
+        <v>6122.5</v>
       </c>
       <c r="I67" t="n">
         <v>6075.212498190082</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.630000000000001</v>
+        <v>-10.06</v>
       </c>
       <c r="L67" t="n">
-        <v>9.619999999999999</v>
+        <v>11.86</v>
       </c>
       <c r="M67" t="n">
         <v>0.4</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.06</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H68" t="n">
-        <v>6124</v>
+        <v>5886.5</v>
       </c>
       <c r="I68" t="n">
         <v>5894.43250186805</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K68" t="n">
-        <v>0.02</v>
+        <v>-3.85</v>
       </c>
       <c r="L68" t="n">
         <v>8.43</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>13.45</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H69" t="n">
-        <v>6452</v>
+        <v>6578.5</v>
       </c>
       <c r="I69" t="n">
         <v>6555.598788788601</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.609999999999999</v>
+        <v>-11.76</v>
       </c>
       <c r="L69" t="n">
-        <v>12.12</v>
+        <v>12.46</v>
       </c>
       <c r="M69" t="n">
         <v>3.41</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.61</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H70" t="n">
-        <v>8245</v>
+        <v>8136.5</v>
       </c>
       <c r="I70" t="n">
         <v>8156.816325919428</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K70" t="n">
-        <v>25.33</v>
+        <v>23.68</v>
       </c>
       <c r="L70" t="n">
         <v>2.14</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>7</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>8.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H71" t="n">
-        <v>8254</v>
+        <v>8500</v>
       </c>
       <c r="I71" t="n">
         <v>8306.254247120713</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.44</v>
+        <v>-4.47</v>
       </c>
       <c r="L71" t="n">
-        <v>5.76</v>
+        <v>6.11</v>
       </c>
       <c r="M71" t="n">
         <v>1</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,12 @@
       <c r="Q72" t="n">
         <v>1</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10375,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10385,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10395,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10405,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10415,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10425,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113.1</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="11">
@@ -9596,7 +10465,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.91</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10475,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.3</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10485,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.48</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10495,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65.94</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10505,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.4</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10515,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.79</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10525,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.04</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="21">
@@ -9666,7 +10535,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.96</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="22">
@@ -9676,7 +10545,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10555,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10565,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="25">
@@ -9716,7 +10585,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.86</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="27">
@@ -9726,7 +10595,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -9736,7 +10605,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
